--- a/textbook_examples/mod03_cleaning_excel.xlsx
+++ b/textbook_examples/mod03_cleaning_excel.xlsx
@@ -1,15 +1,33 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30417"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10817"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_2EC58D42972F256C2DD3C8734E5ED87656CD7F61" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B7ADA528-6EDB-4AF7-B27D-1A6F6397E802}"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://usaskca1-my.sharepoint.com/personal/pjs998_usask_ca/Documents/Teaching/261/2026/textbook_261/textbook_examples/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="175" documentId="11_2EC58D42972F256C2DD3C8734E5ED87656CD7F61" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{934E9118-83A8-6743-ABF7-05AAAC734369}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="0" windowHeight="0" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="620" windowWidth="38400" windowHeight="20980" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Cleaning" sheetId="1" r:id="rId1"/>
+    <sheet name="Raw" sheetId="3" r:id="rId1"/>
+    <sheet name="Checking" sheetId="2" r:id="rId2"/>
+    <sheet name="Cleaning" sheetId="1" r:id="rId3"/>
   </sheets>
+  <externalReferences>
+    <externalReference r:id="rId4"/>
+  </externalReferences>
+  <definedNames>
+    <definedName name="_xlchart.v1.0" hidden="1">Checking!$F$5:$F$23</definedName>
+    <definedName name="_xlchart.v1.1" hidden="1">Checking!$E$5:$E$23</definedName>
+    <definedName name="_xlchart.v1.2" hidden="1">Checking!$G$19:$G$23</definedName>
+    <definedName name="_xlchart.v1.3" hidden="1">Checking!$G$4:$G$18</definedName>
+    <definedName name="_xlchart.v1.4" hidden="1">Checking!$F$19:$F$23</definedName>
+    <definedName name="_xlchart.v1.5" hidden="1">Checking!$F$4:$F$18</definedName>
+  </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -30,8 +48,30 @@
 </workbook>
 </file>
 
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="227" uniqueCount="80">
   <si>
     <t>Cleaning a messy file in Excel</t>
   </si>
@@ -229,13 +269,55 @@
   </si>
   <si>
     <t>Tickets entered more than once</t>
+  </si>
+  <si>
+    <t>Min</t>
+  </si>
+  <si>
+    <t>Max</t>
+  </si>
+  <si>
+    <t>Mean</t>
+  </si>
+  <si>
+    <t>Crop</t>
+  </si>
+  <si>
+    <t>Count</t>
+  </si>
+  <si>
+    <t>Summary statistics of numeric variables</t>
+  </si>
+  <si>
+    <t>St dev</t>
+  </si>
+  <si>
+    <t>Count of crops</t>
+  </si>
+  <si>
+    <t>Count of rows</t>
+  </si>
+  <si>
+    <t>Number of rows</t>
+  </si>
+  <si>
+    <t>Numer of unique rows</t>
+  </si>
+  <si>
+    <t>duplicate_ticket?</t>
+  </si>
+  <si>
+    <t>NA values</t>
+  </si>
+  <si>
+    <t>Blanks</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7">
+  <fonts count="14" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -248,36 +330,86 @@
       <sz val="14"/>
       <color rgb="FF4A7C59"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF5C6B62"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF24302A"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF2F5D46"/>
       <name val="Consolas"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color rgb="FF4A7C59"/>
       <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF24302A"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF2F5D46"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF5C6B62"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF24302A"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -294,6 +426,18 @@
         <fgColor rgb="FFF6EFD9"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-4.9989318521683403E-2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -307,7 +451,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -319,7 +463,26 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -335,6 +498,2150 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chartEx1.xml><?xml version="1.0" encoding="utf-8"?>
+<cx:chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex">
+  <cx:chartData>
+    <cx:data id="0">
+      <cx:numDim type="val">
+        <cx:f>_xlchart.v1.1</cx:f>
+      </cx:numDim>
+    </cx:data>
+  </cx:chartData>
+  <cx:chart>
+    <cx:title pos="t" align="ctr" overlay="0">
+      <cx:tx>
+        <cx:txData>
+          <cx:v>Histogram of weight</cx:v>
+        </cx:txData>
+      </cx:tx>
+      <cx:txPr>
+        <a:bodyPr spcFirstLastPara="1" vertOverflow="ellipsis" horzOverflow="overflow" wrap="square" lIns="0" tIns="0" rIns="0" bIns="0" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr" rtl="0">
+            <a:defRPr/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-US" sz="1400" b="0" i="0" u="none" strike="noStrike" baseline="0">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:sysClr>
+              </a:solidFill>
+              <a:latin typeface="Calibri"/>
+            </a:rPr>
+            <a:t>Histogram of weight</a:t>
+          </a:r>
+        </a:p>
+      </cx:txPr>
+    </cx:title>
+    <cx:plotArea>
+      <cx:plotAreaRegion>
+        <cx:series layoutId="clusteredColumn" uniqueId="{00000000-89DD-7D42-8EE9-555B5DDC6195}">
+          <cx:dataPt idx="0"/>
+          <cx:dataId val="0"/>
+          <cx:layoutPr>
+            <cx:binning intervalClosed="r" underflow="auto" overflow="auto"/>
+          </cx:layoutPr>
+        </cx:series>
+      </cx:plotAreaRegion>
+      <cx:axis id="0">
+        <cx:catScaling gapWidth="0"/>
+        <cx:tickLabels/>
+      </cx:axis>
+      <cx:axis id="1">
+        <cx:valScaling/>
+        <cx:majorGridlines/>
+        <cx:tickLabels/>
+      </cx:axis>
+    </cx:plotArea>
+  </cx:chart>
+</cx:chartSpace>
+</file>
+
+<file path=xl/charts/chartEx2.xml><?xml version="1.0" encoding="utf-8"?>
+<cx:chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex">
+  <cx:chartData>
+    <cx:data id="0">
+      <cx:numDim type="val">
+        <cx:f>_xlchart.v1.0</cx:f>
+      </cx:numDim>
+    </cx:data>
+  </cx:chartData>
+  <cx:chart>
+    <cx:title pos="t" align="ctr" overlay="0">
+      <cx:tx>
+        <cx:txData>
+          <cx:v>HIstogram of moisture_pct</cx:v>
+        </cx:txData>
+      </cx:tx>
+      <cx:txPr>
+        <a:bodyPr spcFirstLastPara="1" vertOverflow="ellipsis" horzOverflow="overflow" wrap="square" lIns="0" tIns="0" rIns="0" bIns="0" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr" rtl="0">
+            <a:defRPr/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-US" sz="1400" b="0" i="0" u="none" strike="noStrike" baseline="0">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:sysClr>
+              </a:solidFill>
+              <a:latin typeface="Calibri"/>
+            </a:rPr>
+            <a:t>HIstogram of moisture_pct</a:t>
+          </a:r>
+        </a:p>
+      </cx:txPr>
+      <cx:extLst>
+        <cx:ext uri="ext:featex">
+          <cx:featureExtension feature="mp" drop="onModelChange">
+            <cx:offset top="0.0555555559694767" left="0.055555582046508789"/>
+          </cx:featureExtension>
+        </cx:ext>
+      </cx:extLst>
+    </cx:title>
+    <cx:plotArea>
+      <cx:plotAreaRegion>
+        <cx:series layoutId="clusteredColumn" uniqueId="{00000000-EC73-434A-BC4C-3AEBBD61B70C}">
+          <cx:dataId val="0"/>
+          <cx:layoutPr>
+            <cx:binning intervalClosed="r" underflow="1" overflow="auto"/>
+          </cx:layoutPr>
+        </cx:series>
+      </cx:plotAreaRegion>
+      <cx:axis id="0">
+        <cx:catScaling gapWidth="0"/>
+        <cx:tickLabels/>
+      </cx:axis>
+      <cx:axis id="1">
+        <cx:valScaling/>
+        <cx:majorGridlines/>
+        <cx:tickLabels/>
+      </cx:axis>
+    </cx:plotArea>
+  </cx:chart>
+</cx:chartSpace>
+</file>
+
+<file path=xl/charts/chartEx3.xml><?xml version="1.0" encoding="utf-8"?>
+<cx:chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex">
+  <cx:chartData>
+    <cx:data id="0">
+      <cx:numDim type="val">
+        <cx:f>_xlchart.v1.2</cx:f>
+      </cx:numDim>
+    </cx:data>
+  </cx:chartData>
+  <cx:chart>
+    <cx:title pos="t" align="ctr" overlay="0">
+      <cx:tx>
+        <cx:txData>
+          <cx:v>HIstogram of grade</cx:v>
+        </cx:txData>
+      </cx:tx>
+      <cx:txPr>
+        <a:bodyPr spcFirstLastPara="1" vertOverflow="ellipsis" horzOverflow="overflow" wrap="square" lIns="0" tIns="0" rIns="0" bIns="0" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr" rtl="0">
+            <a:defRPr/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-US" sz="1400" b="0" i="0" u="none" strike="noStrike" baseline="0">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:sysClr>
+              </a:solidFill>
+              <a:latin typeface="Calibri"/>
+            </a:rPr>
+            <a:t>HIstogram of grade</a:t>
+          </a:r>
+        </a:p>
+      </cx:txPr>
+    </cx:title>
+    <cx:plotArea>
+      <cx:plotAreaRegion>
+        <cx:series layoutId="clusteredColumn" uniqueId="{00000000-8465-7D47-BEB8-010ACDA53A26}">
+          <cx:tx>
+            <cx:txData>
+              <cx:f>_xlchart.v1.3</cx:f>
+              <cx:v>grade 3 2 3 2 3 2 3 2 1 3 2 2 1 N/A</cx:v>
+            </cx:txData>
+          </cx:tx>
+          <cx:dataId val="0"/>
+          <cx:layoutPr>
+            <cx:binning intervalClosed="r">
+              <cx:binCount val="3"/>
+            </cx:binning>
+          </cx:layoutPr>
+        </cx:series>
+      </cx:plotAreaRegion>
+      <cx:axis id="0">
+        <cx:catScaling gapWidth="0"/>
+        <cx:tickLabels/>
+      </cx:axis>
+      <cx:axis id="1">
+        <cx:valScaling/>
+        <cx:majorGridlines/>
+        <cx:tickLabels/>
+      </cx:axis>
+    </cx:plotArea>
+  </cx:chart>
+</cx:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="366">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat">
+        <a:solidFill>
+          <a:srgbClr val="D9D9D9"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDash"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="366">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat">
+        <a:solidFill>
+          <a:srgbClr val="D9D9D9"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDash"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="366">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat">
+        <a:solidFill>
+          <a:srgbClr val="D9D9D9"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDash"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>717550</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>577850</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:to>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" Requires="cx1">
+        <xdr:graphicFrame macro="">
+          <xdr:nvGraphicFramePr>
+            <xdr:cNvPr id="2" name="Chart 1">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A671AE36-1BD9-505E-46AF-63329C7770FE}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvGraphicFramePr/>
+          </xdr:nvGraphicFramePr>
+          <xdr:xfrm>
+            <a:off x="0" y="0"/>
+            <a:ext cx="0" cy="0"/>
+          </xdr:xfrm>
+          <a:graphic>
+            <a:graphicData uri="http://schemas.microsoft.com/office/drawing/2014/chartex">
+              <cx:chart xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+            </a:graphicData>
+          </a:graphic>
+        </xdr:graphicFrame>
+      </mc:Choice>
+      <mc:Fallback>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="0" name=""/>
+            <xdr:cNvSpPr>
+              <a:spLocks noTextEdit="1"/>
+            </xdr:cNvSpPr>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="10712450" y="1384300"/>
+              <a:ext cx="4572000" cy="2743200"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:prstClr val="white"/>
+            </a:solidFill>
+            <a:ln w="1">
+              <a:solidFill>
+                <a:prstClr val="green"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:r>
+                <a:rPr lang="en-US" sz="1100"/>
+                <a:t>This chart isn't available in your version of Excel.
+Editing this shape or saving this workbook into a different file format will permanently break the chart.</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>736600</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>50800</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>596900</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>127000</xdr:rowOff>
+    </xdr:to>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" Requires="cx1">
+        <xdr:graphicFrame macro="">
+          <xdr:nvGraphicFramePr>
+            <xdr:cNvPr id="3" name="Chart 2">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9A5DAB8A-DA1F-C43E-1078-EB57E270A03D}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvGraphicFramePr/>
+          </xdr:nvGraphicFramePr>
+          <xdr:xfrm>
+            <a:off x="0" y="0"/>
+            <a:ext cx="0" cy="0"/>
+          </xdr:xfrm>
+          <a:graphic>
+            <a:graphicData uri="http://schemas.microsoft.com/office/drawing/2014/chartex">
+              <cx:chart xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+            </a:graphicData>
+          </a:graphic>
+        </xdr:graphicFrame>
+      </mc:Choice>
+      <mc:Fallback>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="0" name=""/>
+            <xdr:cNvSpPr>
+              <a:spLocks noTextEdit="1"/>
+            </xdr:cNvSpPr>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="10731500" y="4254500"/>
+              <a:ext cx="4572000" cy="2743200"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:prstClr val="white"/>
+            </a:solidFill>
+            <a:ln w="1">
+              <a:solidFill>
+                <a:prstClr val="green"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:r>
+                <a:rPr lang="en-US" sz="1100"/>
+                <a:t>This chart isn't available in your version of Excel.
+Editing this shape or saving this workbook into a different file format will permanently break the chart.</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>825500</xdr:colOff>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>76200</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>12700</xdr:colOff>
+      <xdr:row>48</xdr:row>
+      <xdr:rowOff>152400</xdr:rowOff>
+    </xdr:to>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" Requires="cx1">
+        <xdr:graphicFrame macro="">
+          <xdr:nvGraphicFramePr>
+            <xdr:cNvPr id="4" name="Chart 3">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{34EE642F-6E39-39F6-C1A5-F6F3395F75D7}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvGraphicFramePr/>
+          </xdr:nvGraphicFramePr>
+          <xdr:xfrm>
+            <a:off x="0" y="0"/>
+            <a:ext cx="0" cy="0"/>
+          </xdr:xfrm>
+          <a:graphic>
+            <a:graphicData uri="http://schemas.microsoft.com/office/drawing/2014/chartex">
+              <cx:chart xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
+            </a:graphicData>
+          </a:graphic>
+        </xdr:graphicFrame>
+      </mc:Choice>
+      <mc:Fallback>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="0" name=""/>
+            <xdr:cNvSpPr>
+              <a:spLocks noTextEdit="1"/>
+            </xdr:cNvSpPr>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="10820400" y="7137400"/>
+              <a:ext cx="4572000" cy="2743200"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:prstClr val="white"/>
+            </a:solidFill>
+            <a:ln w="1">
+              <a:solidFill>
+                <a:prstClr val="green"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:r>
+                <a:rPr lang="en-US" sz="1100"/>
+                <a:t>This chart isn't available in your version of Excel.
+Editing this shape or saving this workbook into a different file format will permanently break the chart.</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Config"/>
+      <sheetName val="Wilcoxon Table"/>
+      <sheetName val="Mann Table"/>
+      <sheetName val="RSign Table"/>
+      <sheetName val="Runs Table"/>
+      <sheetName val="KS Table"/>
+      <sheetName val="KS2 Table"/>
+      <sheetName val="Lil Table"/>
+      <sheetName val="AD Table"/>
+      <sheetName val="AD2 Table"/>
+      <sheetName val="SW Table"/>
+      <sheetName val="Stud. Q Table"/>
+      <sheetName val="Stud. Q Table 2"/>
+      <sheetName val="Sp Rho Table"/>
+      <sheetName val="Ken Tau Table"/>
+      <sheetName val="Durbin Table"/>
+      <sheetName val="Dunnett Table"/>
+      <sheetName val="Dunnett 1"/>
+      <sheetName val="Prime"/>
+      <sheetName val="MSSD"/>
+      <sheetName val="Dict"/>
+      <sheetName val="ADict"/>
+    </sheetNames>
+    <definedNames>
+      <definedName name="MEAN"/>
+    </definedNames>
+    <sheetDataSet>
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3"/>
+      <sheetData sheetId="4"/>
+      <sheetData sheetId="5"/>
+      <sheetData sheetId="6"/>
+      <sheetData sheetId="7"/>
+      <sheetData sheetId="8"/>
+      <sheetData sheetId="9"/>
+      <sheetData sheetId="10"/>
+      <sheetData sheetId="11"/>
+      <sheetData sheetId="12"/>
+      <sheetData sheetId="13"/>
+      <sheetData sheetId="14"/>
+      <sheetData sheetId="15"/>
+      <sheetData sheetId="16"/>
+      <sheetData sheetId="17"/>
+      <sheetData sheetId="18"/>
+      <sheetData sheetId="19"/>
+      <sheetData sheetId="20"/>
+      <sheetData sheetId="21"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -621,9 +2928,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CF3E7FBA-A6BA-1E4E-8C05-5599C8734FB9}">
   <dimension ref="A1:K33"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="13" customWidth="1"/>
@@ -637,12 +2944,12 @@
     <col min="11" max="11" width="28" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:11" ht="18" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:11" ht="57.95" customHeight="1">
+    <row r="2" spans="1:11" ht="58" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="8" t="s">
         <v>1</v>
       </c>
@@ -657,7 +2964,7 @@
       <c r="J2" s="9"/>
       <c r="K2" s="9"/>
     </row>
-    <row r="4" spans="1:11">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
         <v>2</v>
       </c>
@@ -682,6 +2989,1991 @@
       <c r="H4" s="2" t="s">
         <v>9</v>
       </c>
+      <c r="I4" s="18"/>
+      <c r="J4" s="18"/>
+      <c r="K4" s="18"/>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A5" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D5" s="3">
+        <v>44</v>
+      </c>
+      <c r="E5" s="3">
+        <v>10.4</v>
+      </c>
+      <c r="F5" s="3">
+        <v>3</v>
+      </c>
+      <c r="G5" s="3" t="str">
+        <f t="shared" ref="G5:G23" si="0">PROPER(TRIM(C5))</f>
+        <v>Barley</v>
+      </c>
+      <c r="H5" s="3">
+        <f t="shared" ref="H5:H23" si="1">IF(ISNUMBER(E5),IF(E5&lt;1,E5*100,E5),"")</f>
+        <v>10.4</v>
+      </c>
+      <c r="I5" s="25"/>
+      <c r="J5" s="25"/>
+      <c r="K5" s="26"/>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A6" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D6" s="3">
+        <v>38</v>
+      </c>
+      <c r="E6" s="3">
+        <v>10.199999999999999</v>
+      </c>
+      <c r="F6" s="3">
+        <v>2</v>
+      </c>
+      <c r="G6" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>Barley</v>
+      </c>
+      <c r="H6" s="3">
+        <f t="shared" si="1"/>
+        <v>10.199999999999999</v>
+      </c>
+      <c r="I6" s="25"/>
+      <c r="J6" s="25"/>
+      <c r="K6" s="26"/>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A7" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D7" s="3">
+        <v>34.700000000000003</v>
+      </c>
+      <c r="E7" s="3">
+        <v>7</v>
+      </c>
+      <c r="F7" s="3">
+        <v>3</v>
+      </c>
+      <c r="G7" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>Canola</v>
+      </c>
+      <c r="H7" s="3">
+        <f t="shared" si="1"/>
+        <v>7</v>
+      </c>
+      <c r="I7" s="25"/>
+      <c r="J7" s="25"/>
+      <c r="K7" s="26"/>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A8" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="D8" s="3">
+        <v>-12.4</v>
+      </c>
+      <c r="E8" s="3">
+        <v>9.6999999999999993</v>
+      </c>
+      <c r="F8" s="3">
+        <v>2</v>
+      </c>
+      <c r="G8" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>Spring Wheat</v>
+      </c>
+      <c r="H8" s="3">
+        <f t="shared" si="1"/>
+        <v>9.6999999999999993</v>
+      </c>
+      <c r="I8" s="25"/>
+      <c r="J8" s="25"/>
+      <c r="K8" s="26"/>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A9" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="D9" s="3">
+        <v>48.1</v>
+      </c>
+      <c r="E9" s="3"/>
+      <c r="F9" s="3">
+        <v>3</v>
+      </c>
+      <c r="G9" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>Spring Wheat</v>
+      </c>
+      <c r="H9" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="I9" s="25"/>
+      <c r="J9" s="25"/>
+      <c r="K9" s="26"/>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A10" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="D10" s="3">
+        <v>39.200000000000003</v>
+      </c>
+      <c r="E10" s="3">
+        <v>8.1999999999999993</v>
+      </c>
+      <c r="F10" s="3">
+        <v>2</v>
+      </c>
+      <c r="G10" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>Spring Wheat</v>
+      </c>
+      <c r="H10" s="3">
+        <f t="shared" si="1"/>
+        <v>8.1999999999999993</v>
+      </c>
+      <c r="I10" s="25"/>
+      <c r="J10" s="25"/>
+      <c r="K10" s="26"/>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A11" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D11" s="3">
+        <v>42.9</v>
+      </c>
+      <c r="E11" s="3">
+        <v>9.9000000000000005E-2</v>
+      </c>
+      <c r="F11" s="3">
+        <v>3</v>
+      </c>
+      <c r="G11" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>Canola</v>
+      </c>
+      <c r="H11" s="3">
+        <f t="shared" si="1"/>
+        <v>9.9</v>
+      </c>
+      <c r="I11" s="25"/>
+      <c r="J11" s="25"/>
+      <c r="K11" s="26"/>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A12" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D12" s="3">
+        <v>36.5</v>
+      </c>
+      <c r="E12" s="3">
+        <v>11.2</v>
+      </c>
+      <c r="F12" s="3">
+        <v>2</v>
+      </c>
+      <c r="G12" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>Spring Wheat</v>
+      </c>
+      <c r="H12" s="3">
+        <f t="shared" si="1"/>
+        <v>11.2</v>
+      </c>
+      <c r="I12" s="25"/>
+      <c r="J12" s="25"/>
+      <c r="K12" s="26"/>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A13" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="D13" s="3">
+        <v>36.200000000000003</v>
+      </c>
+      <c r="E13" s="3">
+        <v>7.9</v>
+      </c>
+      <c r="F13" s="3">
+        <v>1</v>
+      </c>
+      <c r="G13" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>Spring Wheat</v>
+      </c>
+      <c r="H13" s="3">
+        <f t="shared" si="1"/>
+        <v>7.9</v>
+      </c>
+      <c r="I13" s="25"/>
+      <c r="J13" s="25"/>
+      <c r="K13" s="26"/>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A14" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D14" s="3">
+        <v>41.5</v>
+      </c>
+      <c r="E14" s="3">
+        <v>9.3000000000000007</v>
+      </c>
+      <c r="F14" s="3">
+        <v>3</v>
+      </c>
+      <c r="G14" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>Canola</v>
+      </c>
+      <c r="H14" s="3">
+        <f t="shared" si="1"/>
+        <v>9.3000000000000007</v>
+      </c>
+      <c r="I14" s="25"/>
+      <c r="J14" s="25"/>
+      <c r="K14" s="26"/>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A15" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D15" s="3">
+        <v>33.299999999999997</v>
+      </c>
+      <c r="E15" s="3">
+        <v>11.3</v>
+      </c>
+      <c r="F15" s="3">
+        <v>2</v>
+      </c>
+      <c r="G15" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>Spring Wheat</v>
+      </c>
+      <c r="H15" s="3">
+        <f t="shared" si="1"/>
+        <v>11.3</v>
+      </c>
+      <c r="I15" s="25"/>
+      <c r="J15" s="25"/>
+      <c r="K15" s="26"/>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A16" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D16" s="3">
+        <v>33.200000000000003</v>
+      </c>
+      <c r="E16" s="3">
+        <v>14.6</v>
+      </c>
+      <c r="F16" s="3">
+        <v>2</v>
+      </c>
+      <c r="G16" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>Barley</v>
+      </c>
+      <c r="H16" s="3">
+        <f t="shared" si="1"/>
+        <v>14.6</v>
+      </c>
+      <c r="I16" s="25"/>
+      <c r="J16" s="25"/>
+      <c r="K16" s="26"/>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A17" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="D17" s="3">
+        <v>22.7</v>
+      </c>
+      <c r="E17" s="3">
+        <v>9</v>
+      </c>
+      <c r="F17" s="3">
+        <v>1</v>
+      </c>
+      <c r="G17" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>Spring Wheat</v>
+      </c>
+      <c r="H17" s="3">
+        <f t="shared" si="1"/>
+        <v>9</v>
+      </c>
+      <c r="I17" s="25"/>
+      <c r="J17" s="25"/>
+      <c r="K17" s="26"/>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A18" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="D18" s="3">
+        <v>17.399999999999999</v>
+      </c>
+      <c r="E18" s="3">
+        <v>14.2</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="G18" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>Peas</v>
+      </c>
+      <c r="H18" s="3">
+        <f t="shared" si="1"/>
+        <v>14.2</v>
+      </c>
+      <c r="I18" s="25"/>
+      <c r="J18" s="25"/>
+      <c r="K18" s="26"/>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A19" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="D19" s="3">
+        <v>44.8</v>
+      </c>
+      <c r="E19" s="3">
+        <v>7.5</v>
+      </c>
+      <c r="F19" s="3">
+        <v>3</v>
+      </c>
+      <c r="G19" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>Peas</v>
+      </c>
+      <c r="H19" s="3">
+        <f t="shared" si="1"/>
+        <v>7.5</v>
+      </c>
+      <c r="I19" s="25"/>
+      <c r="J19" s="25"/>
+      <c r="K19" s="26"/>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A20" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="D20" s="3">
+        <v>42.2</v>
+      </c>
+      <c r="E20" s="3">
+        <v>9</v>
+      </c>
+      <c r="F20" s="3">
+        <v>1</v>
+      </c>
+      <c r="G20" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>Peas</v>
+      </c>
+      <c r="H20" s="3">
+        <f t="shared" si="1"/>
+        <v>9</v>
+      </c>
+      <c r="I20" s="25"/>
+      <c r="J20" s="25"/>
+      <c r="K20" s="26"/>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A21" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="D21" s="3">
+        <v>29.5</v>
+      </c>
+      <c r="E21" s="3">
+        <v>9.3000000000000007</v>
+      </c>
+      <c r="F21" s="3">
+        <v>3</v>
+      </c>
+      <c r="G21" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>Barley</v>
+      </c>
+      <c r="H21" s="3">
+        <f t="shared" si="1"/>
+        <v>9.3000000000000007</v>
+      </c>
+      <c r="I21" s="25"/>
+      <c r="J21" s="25"/>
+      <c r="K21" s="26"/>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A22" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="D22" s="3">
+        <v>37.9</v>
+      </c>
+      <c r="E22" s="3">
+        <v>9.1999999999999993</v>
+      </c>
+      <c r="F22" s="3">
+        <v>2</v>
+      </c>
+      <c r="G22" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>Peas</v>
+      </c>
+      <c r="H22" s="3">
+        <f t="shared" si="1"/>
+        <v>9.1999999999999993</v>
+      </c>
+      <c r="I22" s="25"/>
+      <c r="J22" s="25"/>
+      <c r="K22" s="26"/>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A23" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D23" s="3">
+        <v>34.700000000000003</v>
+      </c>
+      <c r="E23" s="3">
+        <v>7</v>
+      </c>
+      <c r="F23" s="3">
+        <v>3</v>
+      </c>
+      <c r="G23" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>Canola</v>
+      </c>
+      <c r="H23" s="3">
+        <f t="shared" si="1"/>
+        <v>7</v>
+      </c>
+      <c r="I23" s="25"/>
+      <c r="J23" s="25"/>
+      <c r="K23" s="26"/>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="G24" s="6"/>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="G25" s="5"/>
+      <c r="H25" s="5"/>
+      <c r="I25" s="5"/>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A27" s="7"/>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A28" s="3"/>
+      <c r="D28" s="3"/>
+      <c r="E28" s="5"/>
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A29" s="3"/>
+      <c r="D29" s="3"/>
+      <c r="E29" s="5"/>
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A30" s="3"/>
+      <c r="D30" s="3"/>
+      <c r="E30" s="5"/>
+    </row>
+    <row r="31" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A31" s="3"/>
+      <c r="D31" s="3"/>
+      <c r="E31" s="5"/>
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A32" s="3"/>
+      <c r="D32" s="3"/>
+      <c r="E32" s="5"/>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A33" s="3"/>
+      <c r="D33" s="3"/>
+      <c r="E33" s="5"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A2:K2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BAACCB21-F825-F849-A176-1BB6C77157A4}">
+  <dimension ref="A1:N60"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="2" max="7" width="15.1640625" customWidth="1"/>
+    <col min="8" max="8" width="16.33203125" customWidth="1"/>
+    <col min="9" max="9" width="15" customWidth="1"/>
+    <col min="10" max="10" width="13" customWidth="1"/>
+    <col min="11" max="11" width="12" customWidth="1"/>
+    <col min="12" max="12" width="28" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:14" ht="18" x14ac:dyDescent="0.2">
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="2:14" ht="58" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B2" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="9"/>
+      <c r="D2" s="9"/>
+      <c r="E2" s="9"/>
+      <c r="F2" s="9"/>
+      <c r="G2" s="9"/>
+      <c r="H2" s="9"/>
+      <c r="I2" s="9"/>
+      <c r="J2" s="9"/>
+      <c r="K2" s="9"/>
+      <c r="L2" s="9"/>
+    </row>
+    <row r="4" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B4" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="I4" s="2"/>
+      <c r="J4" s="18"/>
+      <c r="K4" s="18"/>
+      <c r="L4" s="18"/>
+      <c r="M4" s="12"/>
+      <c r="N4" s="12"/>
+    </row>
+    <row r="5" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B5" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C5" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="D5" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="E5" s="13">
+        <v>44</v>
+      </c>
+      <c r="F5" s="13">
+        <v>10.4</v>
+      </c>
+      <c r="G5" s="13">
+        <v>3</v>
+      </c>
+      <c r="H5" s="4">
+        <f>IF(COUNTIF($B$5:$B5,B5)&gt;1,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="I5" s="19"/>
+      <c r="J5" s="19"/>
+      <c r="K5" s="19"/>
+      <c r="L5" s="20"/>
+      <c r="M5" s="12"/>
+      <c r="N5" s="12"/>
+    </row>
+    <row r="6" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B6" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C6" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="D6" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="E6" s="13">
+        <v>38</v>
+      </c>
+      <c r="F6" s="13">
+        <v>10.199999999999999</v>
+      </c>
+      <c r="G6" s="13">
+        <v>2</v>
+      </c>
+      <c r="H6" s="4">
+        <f>IF(COUNTIF($B$5:$B6,B6)&gt;1,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="I6" s="19"/>
+      <c r="J6" s="19"/>
+      <c r="K6" s="19"/>
+      <c r="L6" s="20"/>
+      <c r="M6" s="12"/>
+      <c r="N6" s="12"/>
+    </row>
+    <row r="7" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B7" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="D7" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E7" s="13">
+        <v>34.700000000000003</v>
+      </c>
+      <c r="F7" s="13">
+        <v>7</v>
+      </c>
+      <c r="G7" s="13">
+        <v>3</v>
+      </c>
+      <c r="H7" s="4">
+        <f>IF(COUNTIF($B$5:$B7,B7)&gt;1,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="I7" s="19"/>
+      <c r="J7" s="19"/>
+      <c r="K7" s="19"/>
+      <c r="L7" s="20"/>
+      <c r="M7" s="12"/>
+      <c r="N7" s="12"/>
+    </row>
+    <row r="8" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B8" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C8" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="D8" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="E8" s="13">
+        <v>-12.4</v>
+      </c>
+      <c r="F8" s="13">
+        <v>9.6999999999999993</v>
+      </c>
+      <c r="G8" s="13">
+        <v>2</v>
+      </c>
+      <c r="H8" s="4">
+        <f>IF(COUNTIF($B$5:$B8,B8)&gt;1,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="I8" s="19"/>
+      <c r="J8" s="19"/>
+      <c r="K8" s="19"/>
+      <c r="L8" s="20"/>
+      <c r="M8" s="12"/>
+      <c r="N8" s="12"/>
+    </row>
+    <row r="9" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B9" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C9" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="D9" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="E9" s="13">
+        <v>48.1</v>
+      </c>
+      <c r="F9" s="13"/>
+      <c r="G9" s="13">
+        <v>3</v>
+      </c>
+      <c r="H9" s="4">
+        <f>IF(COUNTIF($B$5:$B9,B9)&gt;1,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="I9" s="19"/>
+      <c r="J9" s="19"/>
+      <c r="K9" s="19"/>
+      <c r="L9" s="20"/>
+      <c r="M9" s="12"/>
+      <c r="N9" s="12"/>
+    </row>
+    <row r="10" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B10" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C10" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="D10" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="E10" s="13">
+        <v>39.200000000000003</v>
+      </c>
+      <c r="F10" s="13">
+        <v>8.1999999999999993</v>
+      </c>
+      <c r="G10" s="13">
+        <v>2</v>
+      </c>
+      <c r="H10" s="4">
+        <f>IF(COUNTIF($B$5:$B10,B10)&gt;1,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="I10" s="19"/>
+      <c r="J10" s="19"/>
+      <c r="K10" s="19"/>
+      <c r="L10" s="20"/>
+      <c r="M10" s="12"/>
+      <c r="N10" s="12"/>
+    </row>
+    <row r="11" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B11" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C11" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="D11" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="E11" s="13">
+        <v>42.9</v>
+      </c>
+      <c r="F11" s="13">
+        <v>9.9000000000000005E-2</v>
+      </c>
+      <c r="G11" s="13">
+        <v>3</v>
+      </c>
+      <c r="H11" s="4">
+        <f>IF(COUNTIF($B$5:$B11,B11)&gt;1,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="I11" s="19"/>
+      <c r="J11" s="19"/>
+      <c r="K11" s="19"/>
+      <c r="L11" s="20"/>
+      <c r="M11" s="12"/>
+      <c r="N11" s="12"/>
+    </row>
+    <row r="12" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B12" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C12" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="D12" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="E12" s="13">
+        <v>36.5</v>
+      </c>
+      <c r="F12" s="13">
+        <v>11.2</v>
+      </c>
+      <c r="G12" s="13">
+        <v>2</v>
+      </c>
+      <c r="H12" s="4">
+        <f>IF(COUNTIF($B$5:$B12,B12)&gt;1,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="I12" s="19"/>
+      <c r="J12" s="19"/>
+      <c r="K12" s="19"/>
+      <c r="L12" s="20"/>
+      <c r="M12" s="12"/>
+      <c r="N12" s="12"/>
+    </row>
+    <row r="13" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B13" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C13" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="D13" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="E13" s="13">
+        <v>36.200000000000003</v>
+      </c>
+      <c r="F13" s="13">
+        <v>7.9</v>
+      </c>
+      <c r="G13" s="13">
+        <v>1</v>
+      </c>
+      <c r="H13" s="4">
+        <f>IF(COUNTIF($B$5:$B13,B13)&gt;1,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="I13" s="19"/>
+      <c r="J13" s="19"/>
+      <c r="K13" s="19"/>
+      <c r="L13" s="20"/>
+      <c r="M13" s="12"/>
+      <c r="N13" s="12"/>
+    </row>
+    <row r="14" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B14" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="C14" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="D14" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E14" s="13">
+        <v>41.5</v>
+      </c>
+      <c r="F14" s="13">
+        <v>9.3000000000000007</v>
+      </c>
+      <c r="G14" s="13">
+        <v>3</v>
+      </c>
+      <c r="H14" s="4">
+        <f>IF(COUNTIF($B$5:$B14,B14)&gt;1,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="I14" s="19"/>
+      <c r="J14" s="19"/>
+      <c r="K14" s="19"/>
+      <c r="L14" s="20"/>
+      <c r="M14" s="12"/>
+      <c r="N14" s="12"/>
+    </row>
+    <row r="15" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B15" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="C15" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="D15" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="E15" s="13">
+        <v>33.299999999999997</v>
+      </c>
+      <c r="F15" s="13">
+        <v>11.3</v>
+      </c>
+      <c r="G15" s="13">
+        <v>2</v>
+      </c>
+      <c r="H15" s="4">
+        <f>IF(COUNTIF($B$5:$B15,B15)&gt;1,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="I15" s="19"/>
+      <c r="J15" s="19"/>
+      <c r="K15" s="19"/>
+      <c r="L15" s="20"/>
+      <c r="M15" s="12"/>
+      <c r="N15" s="12"/>
+    </row>
+    <row r="16" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B16" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="C16" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="D16" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="E16" s="13">
+        <v>33.200000000000003</v>
+      </c>
+      <c r="F16" s="13">
+        <v>14.6</v>
+      </c>
+      <c r="G16" s="13">
+        <v>2</v>
+      </c>
+      <c r="H16" s="4">
+        <f>IF(COUNTIF($B$5:$B16,B16)&gt;1,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="I16" s="19"/>
+      <c r="J16" s="19"/>
+      <c r="K16" s="19"/>
+      <c r="L16" s="20"/>
+      <c r="M16" s="12"/>
+      <c r="N16" s="12"/>
+    </row>
+    <row r="17" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="B17" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="C17" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="D17" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="E17" s="13">
+        <v>22.7</v>
+      </c>
+      <c r="F17" s="13">
+        <v>9</v>
+      </c>
+      <c r="G17" s="13">
+        <v>1</v>
+      </c>
+      <c r="H17" s="4">
+        <f>IF(COUNTIF($B$5:$B17,B17)&gt;1,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="I17" s="19"/>
+      <c r="J17" s="19"/>
+      <c r="K17" s="19"/>
+      <c r="L17" s="20"/>
+      <c r="M17" s="12"/>
+      <c r="N17" s="12"/>
+    </row>
+    <row r="18" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="B18" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="C18" s="13" t="s">
+        <v>45</v>
+      </c>
+      <c r="D18" s="13" t="s">
+        <v>46</v>
+      </c>
+      <c r="E18" s="13">
+        <v>17.399999999999999</v>
+      </c>
+      <c r="F18" s="13">
+        <v>14.2</v>
+      </c>
+      <c r="G18" s="13" t="s">
+        <v>47</v>
+      </c>
+      <c r="H18" s="4">
+        <f>IF(COUNTIF($B$5:$B18,B18)&gt;1,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="I18" s="19"/>
+      <c r="J18" s="19"/>
+      <c r="K18" s="19"/>
+      <c r="L18" s="20"/>
+      <c r="M18" s="12"/>
+      <c r="N18" s="12"/>
+    </row>
+    <row r="19" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="B19" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="C19" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="D19" s="13" t="s">
+        <v>50</v>
+      </c>
+      <c r="E19" s="13">
+        <v>44.8</v>
+      </c>
+      <c r="F19" s="13">
+        <v>7.5</v>
+      </c>
+      <c r="G19" s="13">
+        <v>3</v>
+      </c>
+      <c r="H19" s="4">
+        <f>IF(COUNTIF($B$5:$B19,B19)&gt;1,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="I19" s="19"/>
+      <c r="J19" s="19"/>
+      <c r="K19" s="19"/>
+      <c r="L19" s="20"/>
+      <c r="M19" s="12"/>
+      <c r="N19" s="12"/>
+    </row>
+    <row r="20" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="B20" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="C20" s="13" t="s">
+        <v>52</v>
+      </c>
+      <c r="D20" s="13" t="s">
+        <v>50</v>
+      </c>
+      <c r="E20" s="13">
+        <v>42.2</v>
+      </c>
+      <c r="F20" s="13">
+        <v>9</v>
+      </c>
+      <c r="G20" s="13">
+        <v>1</v>
+      </c>
+      <c r="H20" s="4">
+        <f>IF(COUNTIF($B$5:$B20,B20)&gt;1,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="I20" s="19"/>
+      <c r="J20" s="19"/>
+      <c r="K20" s="19"/>
+      <c r="L20" s="20"/>
+      <c r="M20" s="12"/>
+      <c r="N20" s="12"/>
+    </row>
+    <row r="21" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="B21" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="C21" s="13" t="s">
+        <v>54</v>
+      </c>
+      <c r="D21" s="13" t="s">
+        <v>55</v>
+      </c>
+      <c r="E21" s="13">
+        <v>29.5</v>
+      </c>
+      <c r="F21" s="13">
+        <v>9.3000000000000007</v>
+      </c>
+      <c r="G21" s="13">
+        <v>3</v>
+      </c>
+      <c r="H21" s="4">
+        <f>IF(COUNTIF($B$5:$B21,B21)&gt;1,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="I21" s="19"/>
+      <c r="J21" s="19"/>
+      <c r="K21" s="19"/>
+      <c r="L21" s="20"/>
+      <c r="M21" s="12"/>
+      <c r="N21" s="12"/>
+    </row>
+    <row r="22" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="B22" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="C22" s="13" t="s">
+        <v>57</v>
+      </c>
+      <c r="D22" s="13" t="s">
+        <v>50</v>
+      </c>
+      <c r="E22" s="13">
+        <v>37.9</v>
+      </c>
+      <c r="F22" s="13">
+        <v>9.1999999999999993</v>
+      </c>
+      <c r="G22" s="13">
+        <v>2</v>
+      </c>
+      <c r="H22" s="4">
+        <f>IF(COUNTIF($B$5:$B22,B22)&gt;1,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="I22" s="19"/>
+      <c r="J22" s="19"/>
+      <c r="K22" s="19"/>
+      <c r="L22" s="20"/>
+      <c r="M22" s="12"/>
+      <c r="N22" s="12"/>
+    </row>
+    <row r="23" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="B23" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C23" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="D23" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E23" s="13">
+        <v>34.700000000000003</v>
+      </c>
+      <c r="F23" s="13">
+        <v>7</v>
+      </c>
+      <c r="G23" s="13">
+        <v>3</v>
+      </c>
+      <c r="H23" s="4">
+        <f>IF(COUNTIF($B$5:$B23,B23)&gt;1,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="I23" s="19"/>
+      <c r="J23" s="19"/>
+      <c r="K23" s="19"/>
+      <c r="L23" s="20"/>
+      <c r="M23" s="12"/>
+      <c r="N23" s="12"/>
+    </row>
+    <row r="24" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="C24" s="12"/>
+      <c r="D24" s="12"/>
+      <c r="E24" s="12"/>
+      <c r="F24" s="12"/>
+      <c r="G24" s="12"/>
+      <c r="H24" s="15"/>
+      <c r="I24" s="12"/>
+      <c r="J24" s="12"/>
+      <c r="K24" s="12"/>
+      <c r="L24" s="12"/>
+      <c r="M24" s="12"/>
+      <c r="N24" s="12"/>
+    </row>
+    <row r="25" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A25" s="21" t="s">
+        <v>71</v>
+      </c>
+      <c r="B25" s="21"/>
+      <c r="C25" s="21"/>
+      <c r="D25" s="21"/>
+      <c r="E25" s="21"/>
+      <c r="F25" s="21"/>
+      <c r="G25" s="21"/>
+      <c r="I25" s="14"/>
+      <c r="J25" s="14"/>
+      <c r="K25" s="12"/>
+      <c r="L25" s="12"/>
+      <c r="M25" s="12"/>
+      <c r="N25" s="12"/>
+    </row>
+    <row r="26" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A26" s="17" t="s">
+        <v>66</v>
+      </c>
+      <c r="B26" s="10"/>
+      <c r="C26" s="11">
+        <f>MIN(D5:D23)</f>
+        <v>0</v>
+      </c>
+      <c r="D26" s="10"/>
+      <c r="E26" s="11">
+        <f>MIN(E5:E23)</f>
+        <v>-12.4</v>
+      </c>
+      <c r="F26" s="11">
+        <f>MIN(F5:F23)</f>
+        <v>9.9000000000000005E-2</v>
+      </c>
+      <c r="G26" s="11">
+        <f>MIN(G5:G23)</f>
+        <v>1</v>
+      </c>
+      <c r="I26" s="12"/>
+      <c r="J26" s="12"/>
+      <c r="K26" s="12"/>
+      <c r="L26" s="12"/>
+      <c r="M26" s="12"/>
+      <c r="N26" s="12"/>
+    </row>
+    <row r="27" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A27" s="17" t="s">
+        <v>67</v>
+      </c>
+      <c r="B27" s="10"/>
+      <c r="C27" s="11">
+        <f>MIN(D6:D24)</f>
+        <v>0</v>
+      </c>
+      <c r="D27" s="10"/>
+      <c r="E27" s="11">
+        <f>MAX(E5:E23)</f>
+        <v>48.1</v>
+      </c>
+      <c r="F27" s="11">
+        <f>MAX(F5:F23)</f>
+        <v>14.6</v>
+      </c>
+      <c r="G27" s="11">
+        <f>MAX(G5:G23)</f>
+        <v>3</v>
+      </c>
+      <c r="I27" s="12"/>
+      <c r="J27" s="12"/>
+      <c r="K27" s="12"/>
+      <c r="L27" s="12"/>
+      <c r="M27" s="12"/>
+      <c r="N27" s="12"/>
+    </row>
+    <row r="28" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A28" s="17" t="s">
+        <v>68</v>
+      </c>
+      <c r="B28" s="10"/>
+      <c r="C28" s="11">
+        <f>MIN(D7:D25)</f>
+        <v>0</v>
+      </c>
+      <c r="D28" s="10"/>
+      <c r="E28" s="11" cm="1">
+        <f t="array" ref="E28">[1]!MEAN(E5:E23)</f>
+        <v>33.915789473684207</v>
+      </c>
+      <c r="F28" s="11" cm="1">
+        <f t="array" ref="F28">[1]!MEAN(F5:F23)</f>
+        <v>9.1721666666666657</v>
+      </c>
+      <c r="G28" s="11" cm="1">
+        <f t="array" ref="G28">[1]!MEAN(G5:G23)</f>
+        <v>2.2777777777777777</v>
+      </c>
+      <c r="I28" s="12"/>
+      <c r="J28" s="12"/>
+      <c r="K28" s="12"/>
+      <c r="L28" s="12"/>
+      <c r="M28" s="12"/>
+      <c r="N28" s="12"/>
+    </row>
+    <row r="29" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A29" s="16" t="s">
+        <v>72</v>
+      </c>
+      <c r="B29" s="10"/>
+      <c r="C29" s="11"/>
+      <c r="D29" s="10"/>
+      <c r="E29" s="11">
+        <f>STDEV(E5:E23)</f>
+        <v>13.469977446070981</v>
+      </c>
+      <c r="F29" s="11">
+        <f>STDEV(F5:F23)</f>
+        <v>3.100609584278172</v>
+      </c>
+      <c r="G29" s="11"/>
+      <c r="I29" s="12"/>
+      <c r="J29" s="12"/>
+      <c r="K29" s="12"/>
+      <c r="L29" s="12"/>
+      <c r="M29" s="12"/>
+      <c r="N29" s="12"/>
+    </row>
+    <row r="30" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A30" s="17" t="s">
+        <v>78</v>
+      </c>
+      <c r="B30" s="11">
+        <f>COUNTIF(B5:B23,"N/A")</f>
+        <v>0</v>
+      </c>
+      <c r="C30" s="11">
+        <f>COUNTIF(C5:C23,"N/A")</f>
+        <v>0</v>
+      </c>
+      <c r="D30" s="11">
+        <f>COUNTIF(D5:D23,"N/A")</f>
+        <v>0</v>
+      </c>
+      <c r="E30" s="11">
+        <f>COUNTIF(E5:E23,"N/A")</f>
+        <v>0</v>
+      </c>
+      <c r="F30" s="11">
+        <f>COUNTIF(F5:F23,"N/A")</f>
+        <v>0</v>
+      </c>
+      <c r="G30" s="11">
+        <f>COUNTIF(G5:G23,"N/A")</f>
+        <v>1</v>
+      </c>
+      <c r="H30" s="12"/>
+      <c r="I30" s="12"/>
+      <c r="J30" s="12"/>
+      <c r="K30" s="12"/>
+      <c r="L30" s="12"/>
+      <c r="M30" s="12"/>
+      <c r="N30" s="12"/>
+    </row>
+    <row r="31" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A31" s="17" t="s">
+        <v>79</v>
+      </c>
+      <c r="B31" s="11">
+        <f t="shared" ref="B31:G31" si="0">COUNTBLANK(B5:B23)</f>
+        <v>0</v>
+      </c>
+      <c r="C31" s="11">
+        <f>COUNTBLANK(C5:C23)</f>
+        <v>0</v>
+      </c>
+      <c r="D31" s="11">
+        <f t="shared" ref="D31:G31" si="1">COUNTBLANK(D5:D23)</f>
+        <v>0</v>
+      </c>
+      <c r="E31" s="11">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="F31" s="11">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="G31" s="11">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H31" s="12"/>
+      <c r="I31" s="12"/>
+      <c r="J31" s="12"/>
+      <c r="K31" s="12"/>
+      <c r="L31" s="12"/>
+      <c r="M31" s="12"/>
+      <c r="N31" s="12"/>
+    </row>
+    <row r="32" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A32" s="19"/>
+      <c r="B32" s="23"/>
+      <c r="C32" s="23"/>
+      <c r="D32" s="24"/>
+      <c r="E32" s="24"/>
+      <c r="F32" s="24"/>
+      <c r="G32" s="24"/>
+      <c r="H32" s="12"/>
+      <c r="I32" s="12"/>
+      <c r="J32" s="12"/>
+      <c r="K32" s="12"/>
+      <c r="L32" s="12"/>
+      <c r="M32" s="12"/>
+      <c r="N32" s="12"/>
+    </row>
+    <row r="33" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="C33" s="12"/>
+      <c r="D33" s="21" t="s">
+        <v>73</v>
+      </c>
+      <c r="E33" s="21"/>
+      <c r="F33" s="12"/>
+      <c r="G33" s="12"/>
+      <c r="H33" s="12"/>
+      <c r="I33" s="12"/>
+      <c r="J33" s="12"/>
+      <c r="K33" s="12"/>
+      <c r="L33" s="12"/>
+      <c r="M33" s="12"/>
+      <c r="N33" s="12"/>
+    </row>
+    <row r="34" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="C34" s="12"/>
+      <c r="D34" s="22" t="s">
+        <v>69</v>
+      </c>
+      <c r="E34" s="22" t="s">
+        <v>70</v>
+      </c>
+      <c r="F34" s="12"/>
+      <c r="G34" s="12"/>
+      <c r="H34" s="12"/>
+      <c r="I34" s="12"/>
+      <c r="J34" s="12"/>
+      <c r="K34" s="12"/>
+      <c r="L34" s="12"/>
+      <c r="M34" s="12"/>
+      <c r="N34" s="12"/>
+    </row>
+    <row r="35" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="C35" s="12"/>
+      <c r="D35" s="11" t="str" cm="1">
+        <f t="array" ref="D35:D39">_xlfn.UNIQUE(D5:D23)</f>
+        <v>barley</v>
+      </c>
+      <c r="E35" s="17">
+        <f>COUNTIF($D$5:$D$23,D35)</f>
+        <v>4</v>
+      </c>
+      <c r="F35" s="12"/>
+      <c r="G35" s="12"/>
+      <c r="H35" s="12"/>
+      <c r="I35" s="12"/>
+      <c r="J35" s="12"/>
+      <c r="K35" s="12"/>
+      <c r="L35" s="12"/>
+      <c r="M35" s="12"/>
+      <c r="N35" s="12"/>
+    </row>
+    <row r="36" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="C36" s="12"/>
+      <c r="D36" s="11" t="str">
+        <v>canola</v>
+      </c>
+      <c r="E36" s="17">
+        <f>COUNTIF($D$5:$D$23,D36)</f>
+        <v>3</v>
+      </c>
+      <c r="F36" s="12"/>
+      <c r="G36" s="12"/>
+      <c r="H36" s="12"/>
+      <c r="I36" s="12"/>
+      <c r="J36" s="12"/>
+      <c r="K36" s="12"/>
+      <c r="L36" s="12"/>
+      <c r="M36" s="12"/>
+      <c r="N36" s="12"/>
+    </row>
+    <row r="37" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="C37" s="12"/>
+      <c r="D37" s="11" t="str">
+        <v>Spring wheat</v>
+      </c>
+      <c r="E37" s="17">
+        <f>COUNTIF($D$5:$D$23,D37)</f>
+        <v>7</v>
+      </c>
+      <c r="F37" s="12"/>
+      <c r="G37" s="12"/>
+      <c r="H37" s="12"/>
+      <c r="I37" s="12"/>
+      <c r="J37" s="12"/>
+      <c r="K37" s="12"/>
+      <c r="L37" s="12"/>
+      <c r="M37" s="12"/>
+      <c r="N37" s="12"/>
+    </row>
+    <row r="38" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="C38" s="12"/>
+      <c r="D38" s="11" t="str">
+        <v xml:space="preserve">Canola </v>
+      </c>
+      <c r="E38" s="17">
+        <f>COUNTIF($D$5:$D$23,D38)</f>
+        <v>1</v>
+      </c>
+      <c r="F38" s="12"/>
+      <c r="G38" s="12"/>
+      <c r="H38" s="12"/>
+      <c r="I38" s="12"/>
+      <c r="J38" s="12"/>
+      <c r="K38" s="12"/>
+      <c r="L38" s="12"/>
+      <c r="M38" s="12"/>
+      <c r="N38" s="12"/>
+    </row>
+    <row r="39" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="C39" s="12"/>
+      <c r="D39" s="11" t="str">
+        <v>peas</v>
+      </c>
+      <c r="E39" s="17">
+        <f>COUNTIF($D$5:$D$23,D39)</f>
+        <v>4</v>
+      </c>
+      <c r="F39" s="12"/>
+      <c r="G39" s="12"/>
+      <c r="H39" s="12"/>
+      <c r="I39" s="12"/>
+      <c r="J39" s="12"/>
+      <c r="K39" s="12"/>
+      <c r="L39" s="12"/>
+      <c r="M39" s="12"/>
+      <c r="N39" s="12"/>
+    </row>
+    <row r="40" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="C40" s="12"/>
+      <c r="D40" s="12"/>
+      <c r="E40" s="12"/>
+      <c r="F40" s="12"/>
+      <c r="G40" s="12"/>
+      <c r="H40" s="12"/>
+      <c r="I40" s="12"/>
+      <c r="J40" s="12"/>
+      <c r="K40" s="12"/>
+      <c r="L40" s="12"/>
+      <c r="M40" s="12"/>
+      <c r="N40" s="12"/>
+    </row>
+    <row r="41" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="C41" s="12"/>
+      <c r="D41" s="12"/>
+      <c r="E41" s="12"/>
+      <c r="F41" s="12"/>
+      <c r="G41" s="12"/>
+      <c r="H41" s="12"/>
+      <c r="I41" s="12"/>
+      <c r="J41" s="12"/>
+      <c r="K41" s="12"/>
+      <c r="L41" s="12"/>
+      <c r="M41" s="12"/>
+      <c r="N41" s="12"/>
+    </row>
+    <row r="42" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="C42" s="12"/>
+      <c r="D42" s="21" t="s">
+        <v>74</v>
+      </c>
+      <c r="E42" s="21"/>
+      <c r="F42" s="12"/>
+      <c r="G42" s="12"/>
+      <c r="H42" s="12"/>
+      <c r="I42" s="12"/>
+      <c r="J42" s="12"/>
+      <c r="K42" s="12"/>
+      <c r="L42" s="12"/>
+      <c r="M42" s="12"/>
+      <c r="N42" s="12"/>
+    </row>
+    <row r="43" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="C43" s="12"/>
+      <c r="D43" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="E43" s="11">
+        <f>ROWS(B5:G23)</f>
+        <v>19</v>
+      </c>
+      <c r="F43" s="12"/>
+      <c r="G43" s="12"/>
+      <c r="H43" s="12"/>
+      <c r="I43" s="12"/>
+      <c r="J43" s="12"/>
+      <c r="K43" s="12"/>
+      <c r="L43" s="12"/>
+      <c r="M43" s="12"/>
+      <c r="N43" s="12"/>
+    </row>
+    <row r="44" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="C44" s="12"/>
+      <c r="D44" s="11" t="s">
+        <v>76</v>
+      </c>
+      <c r="E44" s="11">
+        <f>ROWS(_xlfn.UNIQUE(B5:G23))</f>
+        <v>18</v>
+      </c>
+      <c r="F44" s="12"/>
+      <c r="G44" s="12"/>
+      <c r="H44" s="12"/>
+      <c r="I44" s="12"/>
+      <c r="J44" s="12"/>
+      <c r="K44" s="12"/>
+      <c r="L44" s="12"/>
+      <c r="M44" s="12"/>
+      <c r="N44" s="12"/>
+    </row>
+    <row r="45" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="C45" s="12"/>
+      <c r="D45" s="12"/>
+      <c r="E45" s="12"/>
+      <c r="F45" s="12"/>
+      <c r="G45" s="12"/>
+      <c r="H45" s="12"/>
+      <c r="I45" s="12"/>
+      <c r="J45" s="12"/>
+      <c r="K45" s="12"/>
+      <c r="L45" s="12"/>
+      <c r="M45" s="12"/>
+      <c r="N45" s="12"/>
+    </row>
+    <row r="46" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="C46" s="12"/>
+      <c r="F46" s="12"/>
+      <c r="G46" s="12"/>
+      <c r="H46" s="12"/>
+      <c r="I46" s="12"/>
+      <c r="J46" s="12"/>
+      <c r="K46" s="12"/>
+      <c r="L46" s="12"/>
+      <c r="M46" s="12"/>
+      <c r="N46" s="12"/>
+    </row>
+    <row r="47" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="C47" s="12"/>
+      <c r="F47" s="12"/>
+      <c r="G47" s="12"/>
+      <c r="H47" s="12"/>
+      <c r="I47" s="12"/>
+      <c r="J47" s="12"/>
+      <c r="K47" s="12"/>
+      <c r="L47" s="12"/>
+      <c r="M47" s="12"/>
+      <c r="N47" s="12"/>
+    </row>
+    <row r="48" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="C48" s="12"/>
+      <c r="F48" s="12"/>
+      <c r="G48" s="12"/>
+      <c r="H48" s="12"/>
+      <c r="I48" s="12"/>
+      <c r="J48" s="12"/>
+      <c r="K48" s="12"/>
+      <c r="L48" s="12"/>
+      <c r="M48" s="12"/>
+      <c r="N48" s="12"/>
+    </row>
+    <row r="49" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="C49" s="12"/>
+      <c r="F49" s="12"/>
+      <c r="G49" s="12"/>
+      <c r="H49" s="12"/>
+      <c r="I49" s="12"/>
+      <c r="J49" s="12"/>
+      <c r="K49" s="12"/>
+      <c r="L49" s="12"/>
+      <c r="M49" s="12"/>
+      <c r="N49" s="12"/>
+    </row>
+    <row r="50" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="C50" s="12"/>
+      <c r="F50" s="12"/>
+      <c r="G50" s="12"/>
+      <c r="H50" s="12"/>
+      <c r="I50" s="12"/>
+      <c r="J50" s="12"/>
+      <c r="K50" s="12"/>
+      <c r="L50" s="12"/>
+      <c r="M50" s="12"/>
+      <c r="N50" s="12"/>
+    </row>
+    <row r="51" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="C51" s="12"/>
+      <c r="F51" s="12"/>
+      <c r="G51" s="12"/>
+      <c r="H51" s="12"/>
+      <c r="I51" s="12"/>
+      <c r="J51" s="12"/>
+      <c r="K51" s="12"/>
+      <c r="L51" s="12"/>
+      <c r="M51" s="12"/>
+      <c r="N51" s="12"/>
+    </row>
+    <row r="52" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="C52" s="12"/>
+      <c r="F52" s="12"/>
+      <c r="G52" s="12"/>
+      <c r="H52" s="12"/>
+      <c r="I52" s="12"/>
+      <c r="J52" s="12"/>
+      <c r="K52" s="12"/>
+      <c r="L52" s="12"/>
+      <c r="M52" s="12"/>
+      <c r="N52" s="12"/>
+    </row>
+    <row r="53" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="C53" s="12"/>
+      <c r="F53" s="12"/>
+      <c r="G53" s="12"/>
+      <c r="H53" s="12"/>
+      <c r="I53" s="12"/>
+      <c r="J53" s="12"/>
+      <c r="K53" s="12"/>
+      <c r="L53" s="12"/>
+      <c r="M53" s="12"/>
+      <c r="N53" s="12"/>
+    </row>
+    <row r="54" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="C54" s="12"/>
+      <c r="F54" s="12"/>
+      <c r="G54" s="12"/>
+      <c r="H54" s="12"/>
+      <c r="I54" s="12"/>
+      <c r="J54" s="12"/>
+      <c r="K54" s="12"/>
+      <c r="L54" s="12"/>
+      <c r="M54" s="12"/>
+      <c r="N54" s="12"/>
+    </row>
+    <row r="55" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="C55" s="12"/>
+      <c r="F55" s="12"/>
+      <c r="G55" s="12"/>
+      <c r="H55" s="12"/>
+      <c r="I55" s="12"/>
+      <c r="J55" s="12"/>
+      <c r="K55" s="12"/>
+      <c r="L55" s="12"/>
+      <c r="M55" s="12"/>
+      <c r="N55" s="12"/>
+    </row>
+    <row r="56" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="C56" s="12"/>
+      <c r="F56" s="12"/>
+      <c r="G56" s="12"/>
+      <c r="H56" s="12"/>
+      <c r="I56" s="12"/>
+      <c r="J56" s="12"/>
+      <c r="K56" s="12"/>
+      <c r="L56" s="12"/>
+      <c r="M56" s="12"/>
+      <c r="N56" s="12"/>
+    </row>
+    <row r="57" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="C57" s="12"/>
+      <c r="F57" s="12"/>
+      <c r="G57" s="12"/>
+      <c r="H57" s="12"/>
+      <c r="I57" s="12"/>
+      <c r="J57" s="12"/>
+      <c r="K57" s="12"/>
+      <c r="L57" s="12"/>
+      <c r="M57" s="12"/>
+      <c r="N57" s="12"/>
+    </row>
+    <row r="58" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="C58" s="12"/>
+      <c r="D58" s="12"/>
+      <c r="E58" s="12"/>
+      <c r="F58" s="12"/>
+      <c r="G58" s="12"/>
+      <c r="H58" s="12"/>
+      <c r="I58" s="12"/>
+      <c r="J58" s="12"/>
+      <c r="K58" s="12"/>
+      <c r="L58" s="12"/>
+      <c r="M58" s="12"/>
+      <c r="N58" s="12"/>
+    </row>
+    <row r="59" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="C59" s="12"/>
+      <c r="D59" s="12"/>
+      <c r="E59" s="12"/>
+      <c r="F59" s="12"/>
+      <c r="G59" s="12"/>
+      <c r="H59" s="12"/>
+      <c r="I59" s="12"/>
+      <c r="J59" s="12"/>
+      <c r="K59" s="12"/>
+      <c r="L59" s="12"/>
+      <c r="M59" s="12"/>
+      <c r="N59" s="12"/>
+    </row>
+    <row r="60" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="C60" s="12"/>
+      <c r="D60" s="12"/>
+      <c r="E60" s="12"/>
+      <c r="F60" s="12"/>
+      <c r="G60" s="12"/>
+      <c r="H60" s="12"/>
+      <c r="I60" s="12"/>
+      <c r="J60" s="12"/>
+      <c r="K60" s="12"/>
+      <c r="L60" s="12"/>
+      <c r="M60" s="12"/>
+      <c r="N60" s="12"/>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="B2:L2"/>
+    <mergeCell ref="D33:E33"/>
+    <mergeCell ref="D42:E42"/>
+    <mergeCell ref="A25:G25"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:K33"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="10" customWidth="1"/>
+    <col min="2" max="2" width="13" customWidth="1"/>
+    <col min="3" max="4" width="14" customWidth="1"/>
+    <col min="5" max="5" width="13" customWidth="1"/>
+    <col min="6" max="6" width="7" customWidth="1"/>
+    <col min="7" max="7" width="14" customWidth="1"/>
+    <col min="8" max="8" width="15" customWidth="1"/>
+    <col min="9" max="9" width="13" customWidth="1"/>
+    <col min="10" max="10" width="12" customWidth="1"/>
+    <col min="11" max="11" width="28" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" ht="18" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" ht="58" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="9"/>
+      <c r="C2" s="9"/>
+      <c r="D2" s="9"/>
+      <c r="E2" s="9"/>
+      <c r="F2" s="9"/>
+      <c r="G2" s="9"/>
+      <c r="H2" s="9"/>
+      <c r="I2" s="9"/>
+      <c r="J2" s="9"/>
+      <c r="K2" s="9"/>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A4" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>9</v>
+      </c>
       <c r="I4" s="2" t="s">
         <v>10</v>
       </c>
@@ -692,7 +4984,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:11">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A5" s="3" t="s">
         <v>13</v>
       </c>
@@ -712,11 +5004,11 @@
         <v>3</v>
       </c>
       <c r="G5" s="3" t="str">
-        <f>PROPER(TRIM(C5))</f>
+        <f t="shared" ref="G5:G23" si="0">PROPER(TRIM(C5))</f>
         <v>Barley</v>
       </c>
       <c r="H5" s="3">
-        <f>IF(ISNUMBER(E5),IF(E5&lt;1,E5*100,E5),"")</f>
+        <f t="shared" ref="H5:H23" si="1">IF(ISNUMBER(E5),IF(E5&lt;1,E5*100,E5),"")</f>
         <v>10.4</v>
       </c>
       <c r="I5" s="4">
@@ -724,15 +5016,15 @@
         <v>1</v>
       </c>
       <c r="J5" s="4" t="str">
-        <f>IF(D5&lt;=0,"check","")</f>
+        <f t="shared" ref="J5:J23" si="2">IF(D5&lt;=0,"check","")</f>
         <v/>
       </c>
       <c r="K5" s="5" t="str">
-        <f ca="1">_xlfn.FORMULATEXT(J5)</f>
+        <f t="shared" ref="K5:K23" ca="1" si="3">_xlfn.FORMULATEXT(J5)</f>
         <v>=IF(D5&lt;=0,"check","")</v>
       </c>
     </row>
-    <row r="6" spans="1:11">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A6" s="3" t="s">
         <v>16</v>
       </c>
@@ -752,27 +5044,27 @@
         <v>2</v>
       </c>
       <c r="G6" s="3" t="str">
-        <f>PROPER(TRIM(C6))</f>
+        <f t="shared" si="0"/>
         <v>Barley</v>
       </c>
       <c r="H6" s="3">
-        <f>IF(ISNUMBER(E6),IF(E6&lt;1,E6*100,E6),"")</f>
+        <f t="shared" si="1"/>
         <v>10.199999999999999</v>
       </c>
       <c r="I6" s="4">
-        <f>COUNTIF($A$5:$A$23,A6)</f>
+        <f t="shared" ref="I5:I23" si="4">COUNTIF($A$5:$A$23,A6)</f>
         <v>1</v>
       </c>
       <c r="J6" s="4" t="str">
-        <f>IF(D6&lt;=0,"check","")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="K6" s="5" t="str">
-        <f ca="1">_xlfn.FORMULATEXT(J6)</f>
+        <f t="shared" ca="1" si="3"/>
         <v>=IF(D6&lt;=0,"check","")</v>
       </c>
     </row>
-    <row r="7" spans="1:11">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A7" s="3" t="s">
         <v>18</v>
       </c>
@@ -792,27 +5084,27 @@
         <v>3</v>
       </c>
       <c r="G7" s="3" t="str">
-        <f>PROPER(TRIM(C7))</f>
+        <f t="shared" si="0"/>
         <v>Canola</v>
       </c>
       <c r="H7" s="3">
-        <f>IF(ISNUMBER(E7),IF(E7&lt;1,E7*100,E7),"")</f>
+        <f t="shared" si="1"/>
         <v>7</v>
       </c>
       <c r="I7" s="4">
-        <f>COUNTIF($A$5:$A$23,A7)</f>
+        <f t="shared" si="4"/>
         <v>2</v>
       </c>
       <c r="J7" s="4" t="str">
-        <f>IF(D7&lt;=0,"check","")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="K7" s="5" t="str">
-        <f ca="1">_xlfn.FORMULATEXT(J7)</f>
+        <f t="shared" ca="1" si="3"/>
         <v>=IF(D7&lt;=0,"check","")</v>
       </c>
     </row>
-    <row r="8" spans="1:11">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A8" s="3" t="s">
         <v>21</v>
       </c>
@@ -832,27 +5124,27 @@
         <v>2</v>
       </c>
       <c r="G8" s="3" t="str">
-        <f>PROPER(TRIM(C8))</f>
+        <f t="shared" si="0"/>
         <v>Spring Wheat</v>
       </c>
       <c r="H8" s="3">
-        <f>IF(ISNUMBER(E8),IF(E8&lt;1,E8*100,E8),"")</f>
+        <f t="shared" si="1"/>
         <v>9.6999999999999993</v>
       </c>
       <c r="I8" s="4">
-        <f>COUNTIF($A$5:$A$23,A8)</f>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="J8" s="4" t="str">
-        <f>IF(D8&lt;=0,"check","")</f>
+        <f t="shared" si="2"/>
         <v>check</v>
       </c>
       <c r="K8" s="5" t="str">
-        <f ca="1">_xlfn.FORMULATEXT(J8)</f>
+        <f t="shared" ca="1" si="3"/>
         <v>=IF(D8&lt;=0,"check","")</v>
       </c>
     </row>
-    <row r="9" spans="1:11">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A9" s="3" t="s">
         <v>24</v>
       </c>
@@ -870,27 +5162,27 @@
         <v>3</v>
       </c>
       <c r="G9" s="3" t="str">
-        <f>PROPER(TRIM(C9))</f>
+        <f t="shared" si="0"/>
         <v>Spring Wheat</v>
       </c>
       <c r="H9" s="3" t="str">
-        <f>IF(ISNUMBER(E9),IF(E9&lt;1,E9*100,E9),"")</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="I9" s="4">
-        <f>COUNTIF($A$5:$A$23,A9)</f>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="J9" s="4" t="str">
-        <f>IF(D9&lt;=0,"check","")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="K9" s="5" t="str">
-        <f ca="1">_xlfn.FORMULATEXT(J9)</f>
+        <f t="shared" ca="1" si="3"/>
         <v>=IF(D9&lt;=0,"check","")</v>
       </c>
     </row>
-    <row r="10" spans="1:11">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A10" s="3" t="s">
         <v>26</v>
       </c>
@@ -910,27 +5202,27 @@
         <v>2</v>
       </c>
       <c r="G10" s="3" t="str">
-        <f>PROPER(TRIM(C10))</f>
+        <f t="shared" si="0"/>
         <v>Spring Wheat</v>
       </c>
       <c r="H10" s="3">
-        <f>IF(ISNUMBER(E10),IF(E10&lt;1,E10*100,E10),"")</f>
+        <f t="shared" si="1"/>
         <v>8.1999999999999993</v>
       </c>
       <c r="I10" s="4">
-        <f>COUNTIF($A$5:$A$23,A10)</f>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="J10" s="4" t="str">
-        <f>IF(D10&lt;=0,"check","")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="K10" s="5" t="str">
-        <f ca="1">_xlfn.FORMULATEXT(J10)</f>
+        <f t="shared" ca="1" si="3"/>
         <v>=IF(D10&lt;=0,"check","")</v>
       </c>
     </row>
-    <row r="11" spans="1:11">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A11" s="3" t="s">
         <v>28</v>
       </c>
@@ -950,27 +5242,27 @@
         <v>3</v>
       </c>
       <c r="G11" s="3" t="str">
-        <f>PROPER(TRIM(C11))</f>
+        <f t="shared" si="0"/>
         <v>Canola</v>
       </c>
       <c r="H11" s="3">
-        <f>IF(ISNUMBER(E11),IF(E11&lt;1,E11*100,E11),"")</f>
+        <f t="shared" si="1"/>
         <v>9.9</v>
       </c>
       <c r="I11" s="4">
-        <f>COUNTIF($A$5:$A$23,A11)</f>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="J11" s="4" t="str">
-        <f>IF(D11&lt;=0,"check","")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="K11" s="5" t="str">
-        <f ca="1">_xlfn.FORMULATEXT(J11)</f>
+        <f t="shared" ca="1" si="3"/>
         <v>=IF(D11&lt;=0,"check","")</v>
       </c>
     </row>
-    <row r="12" spans="1:11">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A12" s="3" t="s">
         <v>31</v>
       </c>
@@ -990,27 +5282,27 @@
         <v>2</v>
       </c>
       <c r="G12" s="3" t="str">
-        <f>PROPER(TRIM(C12))</f>
+        <f t="shared" si="0"/>
         <v>Spring Wheat</v>
       </c>
       <c r="H12" s="3">
-        <f>IF(ISNUMBER(E12),IF(E12&lt;1,E12*100,E12),"")</f>
+        <f t="shared" si="1"/>
         <v>11.2</v>
       </c>
       <c r="I12" s="4">
-        <f>COUNTIF($A$5:$A$23,A12)</f>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="J12" s="4" t="str">
-        <f>IF(D12&lt;=0,"check","")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="K12" s="5" t="str">
-        <f ca="1">_xlfn.FORMULATEXT(J12)</f>
+        <f t="shared" ca="1" si="3"/>
         <v>=IF(D12&lt;=0,"check","")</v>
       </c>
     </row>
-    <row r="13" spans="1:11">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A13" s="3" t="s">
         <v>34</v>
       </c>
@@ -1030,27 +5322,27 @@
         <v>1</v>
       </c>
       <c r="G13" s="3" t="str">
-        <f>PROPER(TRIM(C13))</f>
+        <f t="shared" si="0"/>
         <v>Spring Wheat</v>
       </c>
       <c r="H13" s="3">
-        <f>IF(ISNUMBER(E13),IF(E13&lt;1,E13*100,E13),"")</f>
+        <f t="shared" si="1"/>
         <v>7.9</v>
       </c>
       <c r="I13" s="4">
-        <f>COUNTIF($A$5:$A$23,A13)</f>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="J13" s="4" t="str">
-        <f>IF(D13&lt;=0,"check","")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="K13" s="5" t="str">
-        <f ca="1">_xlfn.FORMULATEXT(J13)</f>
+        <f t="shared" ca="1" si="3"/>
         <v>=IF(D13&lt;=0,"check","")</v>
       </c>
     </row>
-    <row r="14" spans="1:11">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A14" s="3" t="s">
         <v>36</v>
       </c>
@@ -1070,27 +5362,27 @@
         <v>3</v>
       </c>
       <c r="G14" s="3" t="str">
-        <f>PROPER(TRIM(C14))</f>
+        <f t="shared" si="0"/>
         <v>Canola</v>
       </c>
       <c r="H14" s="3">
-        <f>IF(ISNUMBER(E14),IF(E14&lt;1,E14*100,E14),"")</f>
+        <f t="shared" si="1"/>
         <v>9.3000000000000007</v>
       </c>
       <c r="I14" s="4">
-        <f>COUNTIF($A$5:$A$23,A14)</f>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="J14" s="4" t="str">
-        <f>IF(D14&lt;=0,"check","")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="K14" s="5" t="str">
-        <f ca="1">_xlfn.FORMULATEXT(J14)</f>
+        <f t="shared" ca="1" si="3"/>
         <v>=IF(D14&lt;=0,"check","")</v>
       </c>
     </row>
-    <row r="15" spans="1:11">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A15" s="3" t="s">
         <v>38</v>
       </c>
@@ -1110,27 +5402,27 @@
         <v>2</v>
       </c>
       <c r="G15" s="3" t="str">
-        <f>PROPER(TRIM(C15))</f>
+        <f t="shared" si="0"/>
         <v>Spring Wheat</v>
       </c>
       <c r="H15" s="3">
-        <f>IF(ISNUMBER(E15),IF(E15&lt;1,E15*100,E15),"")</f>
+        <f t="shared" si="1"/>
         <v>11.3</v>
       </c>
       <c r="I15" s="4">
-        <f>COUNTIF($A$5:$A$23,A15)</f>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="J15" s="4" t="str">
-        <f>IF(D15&lt;=0,"check","")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="K15" s="5" t="str">
-        <f ca="1">_xlfn.FORMULATEXT(J15)</f>
+        <f t="shared" ca="1" si="3"/>
         <v>=IF(D15&lt;=0,"check","")</v>
       </c>
     </row>
-    <row r="16" spans="1:11">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A16" s="3" t="s">
         <v>40</v>
       </c>
@@ -1150,27 +5442,27 @@
         <v>2</v>
       </c>
       <c r="G16" s="3" t="str">
-        <f>PROPER(TRIM(C16))</f>
+        <f t="shared" si="0"/>
         <v>Barley</v>
       </c>
       <c r="H16" s="3">
-        <f>IF(ISNUMBER(E16),IF(E16&lt;1,E16*100,E16),"")</f>
+        <f t="shared" si="1"/>
         <v>14.6</v>
       </c>
       <c r="I16" s="4">
-        <f>COUNTIF($A$5:$A$23,A16)</f>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="J16" s="4" t="str">
-        <f>IF(D16&lt;=0,"check","")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="K16" s="5" t="str">
-        <f ca="1">_xlfn.FORMULATEXT(J16)</f>
+        <f t="shared" ca="1" si="3"/>
         <v>=IF(D16&lt;=0,"check","")</v>
       </c>
     </row>
-    <row r="17" spans="1:11">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A17" s="3" t="s">
         <v>42</v>
       </c>
@@ -1190,27 +5482,27 @@
         <v>1</v>
       </c>
       <c r="G17" s="3" t="str">
-        <f>PROPER(TRIM(C17))</f>
+        <f t="shared" si="0"/>
         <v>Spring Wheat</v>
       </c>
       <c r="H17" s="3">
-        <f>IF(ISNUMBER(E17),IF(E17&lt;1,E17*100,E17),"")</f>
+        <f t="shared" si="1"/>
         <v>9</v>
       </c>
       <c r="I17" s="4">
-        <f>COUNTIF($A$5:$A$23,A17)</f>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="J17" s="4" t="str">
-        <f>IF(D17&lt;=0,"check","")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="K17" s="5" t="str">
-        <f ca="1">_xlfn.FORMULATEXT(J17)</f>
+        <f t="shared" ca="1" si="3"/>
         <v>=IF(D17&lt;=0,"check","")</v>
       </c>
     </row>
-    <row r="18" spans="1:11">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A18" s="3" t="s">
         <v>44</v>
       </c>
@@ -1230,27 +5522,27 @@
         <v>47</v>
       </c>
       <c r="G18" s="3" t="str">
-        <f>PROPER(TRIM(C18))</f>
+        <f t="shared" si="0"/>
         <v>Peas</v>
       </c>
       <c r="H18" s="3">
-        <f>IF(ISNUMBER(E18),IF(E18&lt;1,E18*100,E18),"")</f>
+        <f t="shared" si="1"/>
         <v>14.2</v>
       </c>
       <c r="I18" s="4">
-        <f>COUNTIF($A$5:$A$23,A18)</f>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="J18" s="4" t="str">
-        <f>IF(D18&lt;=0,"check","")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="K18" s="5" t="str">
-        <f ca="1">_xlfn.FORMULATEXT(J18)</f>
+        <f t="shared" ca="1" si="3"/>
         <v>=IF(D18&lt;=0,"check","")</v>
       </c>
     </row>
-    <row r="19" spans="1:11">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A19" s="3" t="s">
         <v>48</v>
       </c>
@@ -1270,27 +5562,27 @@
         <v>3</v>
       </c>
       <c r="G19" s="3" t="str">
-        <f>PROPER(TRIM(C19))</f>
+        <f t="shared" si="0"/>
         <v>Peas</v>
       </c>
       <c r="H19" s="3">
-        <f>IF(ISNUMBER(E19),IF(E19&lt;1,E19*100,E19),"")</f>
+        <f t="shared" si="1"/>
         <v>7.5</v>
       </c>
       <c r="I19" s="4">
-        <f>COUNTIF($A$5:$A$23,A19)</f>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="J19" s="4" t="str">
-        <f>IF(D19&lt;=0,"check","")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="K19" s="5" t="str">
-        <f ca="1">_xlfn.FORMULATEXT(J19)</f>
+        <f t="shared" ca="1" si="3"/>
         <v>=IF(D19&lt;=0,"check","")</v>
       </c>
     </row>
-    <row r="20" spans="1:11">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A20" s="3" t="s">
         <v>51</v>
       </c>
@@ -1310,27 +5602,27 @@
         <v>1</v>
       </c>
       <c r="G20" s="3" t="str">
-        <f>PROPER(TRIM(C20))</f>
+        <f t="shared" si="0"/>
         <v>Peas</v>
       </c>
       <c r="H20" s="3">
-        <f>IF(ISNUMBER(E20),IF(E20&lt;1,E20*100,E20),"")</f>
+        <f t="shared" si="1"/>
         <v>9</v>
       </c>
       <c r="I20" s="4">
-        <f>COUNTIF($A$5:$A$23,A20)</f>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="J20" s="4" t="str">
-        <f>IF(D20&lt;=0,"check","")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="K20" s="5" t="str">
-        <f ca="1">_xlfn.FORMULATEXT(J20)</f>
+        <f t="shared" ca="1" si="3"/>
         <v>=IF(D20&lt;=0,"check","")</v>
       </c>
     </row>
-    <row r="21" spans="1:11">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A21" s="3" t="s">
         <v>53</v>
       </c>
@@ -1350,27 +5642,27 @@
         <v>3</v>
       </c>
       <c r="G21" s="3" t="str">
-        <f>PROPER(TRIM(C21))</f>
+        <f t="shared" si="0"/>
         <v>Barley</v>
       </c>
       <c r="H21" s="3">
-        <f>IF(ISNUMBER(E21),IF(E21&lt;1,E21*100,E21),"")</f>
+        <f t="shared" si="1"/>
         <v>9.3000000000000007</v>
       </c>
       <c r="I21" s="4">
-        <f>COUNTIF($A$5:$A$23,A21)</f>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="J21" s="4" t="str">
-        <f>IF(D21&lt;=0,"check","")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="K21" s="5" t="str">
-        <f ca="1">_xlfn.FORMULATEXT(J21)</f>
+        <f t="shared" ca="1" si="3"/>
         <v>=IF(D21&lt;=0,"check","")</v>
       </c>
     </row>
-    <row r="22" spans="1:11">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A22" s="3" t="s">
         <v>56</v>
       </c>
@@ -1390,27 +5682,27 @@
         <v>2</v>
       </c>
       <c r="G22" s="3" t="str">
-        <f>PROPER(TRIM(C22))</f>
+        <f t="shared" si="0"/>
         <v>Peas</v>
       </c>
       <c r="H22" s="3">
-        <f>IF(ISNUMBER(E22),IF(E22&lt;1,E22*100,E22),"")</f>
+        <f t="shared" si="1"/>
         <v>9.1999999999999993</v>
       </c>
       <c r="I22" s="4">
-        <f>COUNTIF($A$5:$A$23,A22)</f>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="J22" s="4" t="str">
-        <f>IF(D22&lt;=0,"check","")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="K22" s="5" t="str">
-        <f ca="1">_xlfn.FORMULATEXT(J22)</f>
+        <f t="shared" ca="1" si="3"/>
         <v>=IF(D22&lt;=0,"check","")</v>
       </c>
     </row>
-    <row r="23" spans="1:11">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A23" s="3" t="s">
         <v>18</v>
       </c>
@@ -1430,32 +5722,32 @@
         <v>3</v>
       </c>
       <c r="G23" s="3" t="str">
-        <f>PROPER(TRIM(C23))</f>
+        <f t="shared" si="0"/>
         <v>Canola</v>
       </c>
       <c r="H23" s="3">
-        <f>IF(ISNUMBER(E23),IF(E23&lt;1,E23*100,E23),"")</f>
+        <f t="shared" si="1"/>
         <v>7</v>
       </c>
       <c r="I23" s="4">
-        <f>COUNTIF($A$5:$A$23,A23)</f>
+        <f t="shared" si="4"/>
         <v>2</v>
       </c>
       <c r="J23" s="4" t="str">
-        <f>IF(D23&lt;=0,"check","")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="K23" s="5" t="str">
-        <f ca="1">_xlfn.FORMULATEXT(J23)</f>
+        <f t="shared" ca="1" si="3"/>
         <v>=IF(D23&lt;=0,"check","")</v>
       </c>
     </row>
-    <row r="24" spans="1:11">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.2">
       <c r="G24" s="6" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="25" spans="1:11">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.2">
       <c r="G25" s="5" t="str">
         <f ca="1">_xlfn.FORMULATEXT(G5)</f>
         <v>=PROPER(TRIM(C5))</v>
@@ -1469,12 +5761,12 @@
         <v>=COUNTIF($A$5:$A$23,A5)</v>
       </c>
     </row>
-    <row r="27" spans="1:11">
+    <row r="27" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A27" s="7" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="28" spans="1:11">
+    <row r="28" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A28" s="3" t="s">
         <v>60</v>
       </c>
@@ -1483,11 +5775,11 @@
         <v>-12.4</v>
       </c>
       <c r="E28" s="5" t="str">
-        <f ca="1">_xlfn.FORMULATEXT(D28)</f>
+        <f t="shared" ref="E28:E33" ca="1" si="5">_xlfn.FORMULATEXT(D28)</f>
         <v>=MIN(D5:D23)</v>
       </c>
     </row>
-    <row r="29" spans="1:11">
+    <row r="29" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A29" s="3" t="s">
         <v>61</v>
       </c>
@@ -1496,11 +5788,11 @@
         <v>14.6</v>
       </c>
       <c r="E29" s="5" t="str">
-        <f ca="1">_xlfn.FORMULATEXT(D29)</f>
+        <f t="shared" ca="1" si="5"/>
         <v>=MAX(E5:E23)</v>
       </c>
     </row>
-    <row r="30" spans="1:11">
+    <row r="30" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A30" s="3" t="s">
         <v>62</v>
       </c>
@@ -1509,11 +5801,11 @@
         <v>9.9000000000000005E-2</v>
       </c>
       <c r="E30" s="5" t="str">
-        <f ca="1">_xlfn.FORMULATEXT(D30)</f>
+        <f t="shared" ca="1" si="5"/>
         <v>=MIN(E5:E23)</v>
       </c>
     </row>
-    <row r="31" spans="1:11">
+    <row r="31" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A31" s="3" t="s">
         <v>63</v>
       </c>
@@ -1522,11 +5814,11 @@
         <v>1</v>
       </c>
       <c r="E31" s="5" t="str">
-        <f ca="1">_xlfn.FORMULATEXT(D31)</f>
+        <f t="shared" ca="1" si="5"/>
         <v>=COUNTBLANK(E5:E23)</v>
       </c>
     </row>
-    <row r="32" spans="1:11">
+    <row r="32" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A32" s="3" t="s">
         <v>64</v>
       </c>
@@ -1535,11 +5827,11 @@
         <v>0</v>
       </c>
       <c r="E32" s="5" t="str">
-        <f ca="1">_xlfn.FORMULATEXT(D32)</f>
+        <f t="shared" ca="1" si="5"/>
         <v>=SUMPRODUCT(--ISTEXT(E5:E23))</v>
       </c>
     </row>
-    <row r="33" spans="1:5">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A33" s="3" t="s">
         <v>65</v>
       </c>
@@ -1548,7 +5840,7 @@
         <v>1</v>
       </c>
       <c r="E33" s="5" t="str">
-        <f ca="1">_xlfn.FORMULATEXT(D33)</f>
+        <f t="shared" ca="1" si="5"/>
         <v>=SUMPRODUCT(--(I5:I23&gt;1))/2</v>
       </c>
     </row>
